--- a/docs/اختبار المتوسطه.xlsx
+++ b/docs/اختبار المتوسطه.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\MA-Waves\MA-Waves\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0E61B284-564F-4727-9A8F-14581E481794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC8F33C1-4110-4C22-8B90-FEF7B931BD26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{7819BD92-4B63-487D-A2E5-7EFEA3C3CD0C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{7819BD92-4B63-487D-A2E5-7EFEA3C3CD0C}"/>
   </bookViews>
   <sheets>
     <sheet name="هبوط" sheetId="3" r:id="rId1"/>
     <sheet name="صعود" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
+    <sheet name="صعود 2 " sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="51">
   <si>
     <t>#</t>
   </si>
@@ -65,18 +65,12 @@
     <t>صعود</t>
   </si>
   <si>
-    <t>صحيحة</t>
-  </si>
-  <si>
     <t>هبوط</t>
   </si>
   <si>
     <t>كسر ⇒ نعيد العد</t>
   </si>
   <si>
-    <t>قمه صفراء</t>
-  </si>
-  <si>
     <t>الحالة المتوقعه</t>
   </si>
   <si>
@@ -86,60 +80,18 @@
     <t>قاع صغير</t>
   </si>
   <si>
-    <t xml:space="preserve">قمة </t>
-  </si>
-  <si>
-    <t xml:space="preserve">قاع متوسط </t>
-  </si>
-  <si>
     <t>قمه صغيره</t>
   </si>
   <si>
-    <t xml:space="preserve">قمه متوسطه لانها حصل كسر عند 4565.456 القعاعده تقول ادنى سعر قل الكسر قاع متوسط أي ان ادنى قاع هو 4565.457 اذا هذا قاع متوسط واعلى قمه بعد الكسر قمه متوسطه اين اعلى قمنه بعد الكسر هي 4585.244 </t>
-  </si>
-  <si>
     <t>قاع صغيره</t>
   </si>
   <si>
-    <t>قمه</t>
-  </si>
-  <si>
-    <t>قاع متوسط لان القمه التي بعده كسره القمه التي قبله</t>
-  </si>
-  <si>
-    <t>قمه متوسطه وهذا خطا هنا يجب اعاده العد من جديد لم يحدث أي كسر  ❌ لم يصفّر</t>
-  </si>
-  <si>
     <t>قمه صغير</t>
   </si>
   <si>
-    <t xml:space="preserve">قمه متوسطه لانها القمه التي بعد الكسر </t>
-  </si>
-  <si>
-    <t>قمه متوسطه وهذا خاطئ</t>
-  </si>
-  <si>
-    <t>يقمه صغيره</t>
-  </si>
-  <si>
-    <t>قاع متوسط لان القاع الذي قبل الكسر</t>
-  </si>
-  <si>
-    <t>قمه صغيره هذا خاطئ</t>
-  </si>
-  <si>
     <t>قمه متوسطه</t>
   </si>
   <si>
-    <t>قاع متوسط لانه القاع الذي قبل الكسر</t>
-  </si>
-  <si>
-    <t xml:space="preserve">قاع </t>
-  </si>
-  <si>
-    <t>قمه صعيره</t>
-  </si>
-  <si>
     <t>الترتيب</t>
   </si>
   <si>
@@ -149,12 +101,18 @@
     <t>قاع متوسط</t>
   </si>
   <si>
+    <t>قمة صغير</t>
+  </si>
+  <si>
     <t>تصحيح</t>
   </si>
   <si>
     <t>لانه القاع الذي بعد الكسر</t>
   </si>
   <si>
+    <t>Column1</t>
+  </si>
+  <si>
     <t>لانه القمه التي قبل الكسر</t>
   </si>
   <si>
@@ -207,6 +165,21 @@
   </si>
   <si>
     <t>لانها بداية الموجه</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بدايه الموجه </t>
+  </si>
+  <si>
+    <t>قمة متوسطه</t>
+  </si>
+  <si>
+    <t xml:space="preserve">لان القمه التي قبل الكسر كسر   </t>
+  </si>
+  <si>
+    <t>لانها القمه التي قبل الكسر</t>
+  </si>
+  <si>
+    <t>قاع متوسط لانه القاع الذي بعد الكسر</t>
   </si>
 </sst>
 </file>
@@ -352,15 +325,17 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{22CDCE33-A84A-48CD-B8D8-CDE282F69857}" name="Table1" displayName="Table1" ref="A1:F32" totalsRowShown="0">
-  <autoFilter ref="A1:F32" xr:uid="{22CDCE33-A84A-48CD-B8D8-CDE282F69857}"/>
-  <tableColumns count="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{22CDCE33-A84A-48CD-B8D8-CDE282F69857}" name="Table1" displayName="Table1" ref="A1:H32" totalsRowShown="0">
+  <autoFilter ref="A1:H32" xr:uid="{22CDCE33-A84A-48CD-B8D8-CDE282F69857}"/>
+  <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{9A6B6C22-E3E9-4D40-86BA-25D4EEAFF070}" name="#" dataCellStyle="Neutral"/>
+    <tableColumn id="8" xr3:uid="{4755B6E2-47AB-4A08-9F8A-DA0AD56E081E}" name="الترتيب" dataCellStyle="Neutral"/>
     <tableColumn id="2" xr3:uid="{88CD8FDC-6962-4BC9-B9BA-B8DA41EBB722}" name="السعر"/>
     <tableColumn id="3" xr3:uid="{B7C7EC48-0158-44C5-A187-0436A8117E3D}" name="النوع"/>
     <tableColumn id="4" xr3:uid="{AAFA3E1F-233B-4B52-B0CB-3B6BC39B343F}" name="الحدث المتوقع"/>
     <tableColumn id="5" xr3:uid="{FBB4589D-2115-4B95-BBC5-1909283E29D9}" name="الحالة الحالية"/>
     <tableColumn id="6" xr3:uid="{D788DC78-F4BF-4C4F-B0D8-2088F224BE8C}" name="الحالة المتوقعه"/>
+    <tableColumn id="7" xr3:uid="{3FD91210-A580-40E7-935F-598A850A856F}" name="Column1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -677,7 +652,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -692,10 +667,10 @@
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -712,13 +687,13 @@
         <v>6</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -735,10 +710,10 @@
         <v>8</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G3" s="4"/>
     </row>
@@ -756,10 +731,10 @@
         <v>9</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="G4" s="4"/>
     </row>
@@ -777,10 +752,10 @@
         <v>8</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G5" s="4"/>
     </row>
@@ -798,10 +773,10 @@
         <v>10</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="G6" s="4"/>
     </row>
@@ -819,13 +794,13 @@
         <v>8</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -842,13 +817,13 @@
         <v>9</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -862,13 +837,13 @@
         <v>7</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G9" s="4"/>
     </row>
@@ -886,13 +861,13 @@
         <v>9</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -906,13 +881,13 @@
         <v>7</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G11" s="4"/>
     </row>
@@ -930,10 +905,10 @@
         <v>9</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="G12" s="4"/>
     </row>
@@ -948,16 +923,16 @@
         <v>7</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -974,13 +949,13 @@
         <v>9</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -994,13 +969,13 @@
         <v>7</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G15" s="4"/>
     </row>
@@ -1018,13 +993,13 @@
         <v>11</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1038,13 +1013,13 @@
         <v>7</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G17" s="4"/>
     </row>
@@ -1062,10 +1037,10 @@
         <v>9</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="G18" s="4"/>
     </row>
@@ -1083,10 +1058,10 @@
         <v>8</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G19" s="4"/>
     </row>
@@ -1104,10 +1079,10 @@
         <v>9</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="G20" s="4"/>
     </row>
@@ -1122,16 +1097,16 @@
         <v>7</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1145,16 +1120,16 @@
         <v>5</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -1171,13 +1146,13 @@
         <v>9</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1194,13 +1169,13 @@
         <v>11</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1214,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G25" s="4"/>
     </row>
@@ -1238,10 +1213,10 @@
         <v>11</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="G26" s="4"/>
     </row>
@@ -1256,13 +1231,13 @@
         <v>7</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G27" s="4"/>
     </row>
@@ -1277,13 +1252,13 @@
         <v>5</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="G28" s="4"/>
     </row>
@@ -1301,10 +1276,10 @@
         <v>9</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G29" s="4"/>
     </row>
@@ -1320,10 +1295,10 @@
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="G30" s="4"/>
     </row>
@@ -1348,7 +1323,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -1363,10 +1338,10 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G1" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1380,16 +1355,16 @@
         <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1406,10 +1381,10 @@
         <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1423,13 +1398,13 @@
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1446,10 +1421,10 @@
         <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1463,13 +1438,13 @@
         <v>7</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1486,10 +1461,10 @@
         <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1503,13 +1478,13 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1526,13 +1501,13 @@
         <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F9" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="G9" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1546,16 +1521,16 @@
         <v>7</v>
       </c>
       <c r="D10" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F10" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="G10" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1569,16 +1544,16 @@
         <v>5</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="E11" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F11" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G11" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1592,13 +1567,13 @@
         <v>7</v>
       </c>
       <c r="D12" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E12" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F12" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -1615,13 +1590,13 @@
         <v>11</v>
       </c>
       <c r="E13" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="G13" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1635,16 +1610,16 @@
         <v>7</v>
       </c>
       <c r="D14" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E14" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F14" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="G14" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1658,16 +1633,16 @@
         <v>5</v>
       </c>
       <c r="D15" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="E15" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F15" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="G15" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1681,16 +1656,16 @@
         <v>7</v>
       </c>
       <c r="D16" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E16" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="F16" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="G16" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1707,10 +1682,10 @@
         <v>11</v>
       </c>
       <c r="E17" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F17" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1724,13 +1699,13 @@
         <v>7</v>
       </c>
       <c r="D18" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E18" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F18" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1747,10 +1722,10 @@
         <v>11</v>
       </c>
       <c r="E19" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F19" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1764,13 +1739,13 @@
         <v>7</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1787,10 +1762,10 @@
         <v>11</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1810,618 +1785,459 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{493068D4-D9CB-4381-9FD4-D5F2580243C6}">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.85546875" customWidth="1"/>
-    <col min="3" max="3" width="30.42578125" customWidth="1"/>
-    <col min="4" max="4" width="35.42578125" customWidth="1"/>
-    <col min="5" max="5" width="72.7109375" customWidth="1"/>
-    <col min="6" max="6" width="56.7109375" customWidth="1"/>
+    <col min="1" max="2" width="29" customWidth="1"/>
+    <col min="3" max="3" width="16.85546875" customWidth="1"/>
+    <col min="4" max="4" width="46.28515625" customWidth="1"/>
+    <col min="5" max="5" width="35.42578125" customWidth="1"/>
+    <col min="6" max="6" width="72.7109375" customWidth="1"/>
+    <col min="7" max="7" width="56.7109375" customWidth="1"/>
+    <col min="8" max="8" width="26.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="5">
+      <c r="G1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>4780.9530000000004</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="D2" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6">
+        <v>49716.51</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6">
+        <v>51309.57</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1">
+        <v>3</v>
+      </c>
+      <c r="C5" s="6">
+        <v>50851.87</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1">
+        <v>4</v>
+      </c>
+      <c r="C6" s="6">
+        <v>51948.21</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1">
+        <v>5</v>
+      </c>
+      <c r="C7" s="6">
+        <v>51646.63</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B8" s="1">
+        <v>6</v>
+      </c>
+      <c r="C8" s="6">
+        <v>52203.67</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9" s="1">
+        <v>7</v>
+      </c>
+      <c r="C9" s="6">
+        <v>51944.66</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1">
+        <v>8</v>
+      </c>
+      <c r="C10" s="6">
+        <v>52274.63</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" s="1">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>51416.01</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12" s="1">
+        <v>10</v>
+      </c>
+      <c r="C12" s="6">
+        <v>51865.63</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
+      <c r="B13" s="1">
+        <v>11</v>
+      </c>
+      <c r="C13" s="6">
+        <v>51376.98</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>12</v>
+      </c>
+      <c r="B14" s="1">
+        <v>12</v>
+      </c>
+      <c r="C14" s="6">
+        <v>51593.41</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>13</v>
+      </c>
+      <c r="B15" s="1">
+        <v>13</v>
+      </c>
+      <c r="C15" s="6">
+        <v>51302.47</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>14</v>
+      </c>
+      <c r="B16" s="1">
+        <v>14</v>
+      </c>
+      <c r="C16" s="6">
+        <v>51905.63</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="F2" t="s">
+      <c r="B17" s="1">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="5">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>4634.4539999999997</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="C17" s="6">
+        <v>51290</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>16</v>
+      </c>
+      <c r="B18" s="1">
+        <v>16</v>
+      </c>
+      <c r="C18" s="6">
+        <v>51887.89</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>17</v>
+      </c>
+      <c r="B19" s="1">
+        <v>17</v>
+      </c>
+      <c r="C19" s="6">
+        <v>51543.74</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="F3" t="s">
+      <c r="B20" s="1">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>4726.7359999999999</v>
-      </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>4510.8729999999996</v>
-      </c>
-      <c r="C5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="5">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>4565.4570000000003</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="C20" s="6">
+        <v>52249.79</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" t="s">
         <v>19</v>
       </c>
-      <c r="D6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="5">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>4482.1869999999999</v>
-      </c>
-      <c r="C7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" t="s">
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>19</v>
+      </c>
+      <c r="B21" s="1">
+        <v>19</v>
+      </c>
+      <c r="C21" s="6">
+        <v>51743.360000000001</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="F7" t="s">
+      <c r="B22" s="1">
         <v>20</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="5">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>4585.2439999999997</v>
-      </c>
-      <c r="C8" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="5">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>4533.7529999999997</v>
-      </c>
-      <c r="C9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="5">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>4589.9660000000003</v>
-      </c>
-      <c r="C10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" t="s">
-        <v>26</v>
-      </c>
-      <c r="F10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="5">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>4530.585</v>
-      </c>
-      <c r="C11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" t="s">
-        <v>18</v>
-      </c>
-      <c r="F11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="5">
-        <v>11</v>
-      </c>
-      <c r="B12">
-        <v>4558.6260000000002</v>
-      </c>
-      <c r="C12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" t="s">
-        <v>21</v>
-      </c>
-      <c r="F12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="5">
-        <v>12</v>
-      </c>
-      <c r="B13">
-        <v>4452.1949999999997</v>
-      </c>
-      <c r="C13" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="5">
-        <v>13</v>
-      </c>
-      <c r="B14">
-        <v>4570.326</v>
-      </c>
-      <c r="C14" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" t="s">
-        <v>27</v>
-      </c>
-      <c r="F14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15">
-        <v>4485.1710000000003</v>
-      </c>
-      <c r="C15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" t="s">
-        <v>18</v>
-      </c>
-      <c r="F15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="5">
-        <v>15</v>
-      </c>
-      <c r="B16" s="5">
-        <v>4583.6980000000003</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="5">
-        <v>16</v>
-      </c>
-      <c r="B17">
-        <v>4487.9549999999999</v>
-      </c>
-      <c r="C17" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F17" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="5">
+      <c r="C22" s="6">
+        <v>52672.65</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" t="s">
         <v>17</v>
       </c>
-      <c r="B18">
-        <v>4537.5569999999998</v>
-      </c>
-      <c r="C18" t="s">
-        <v>5</v>
-      </c>
-      <c r="D18" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" t="s">
-        <v>30</v>
-      </c>
-      <c r="F18" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="5">
-        <v>18</v>
-      </c>
-      <c r="B19" s="5">
-        <v>4401.4399999999996</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="5">
-        <v>19</v>
-      </c>
-      <c r="B20">
-        <v>4476.4189999999999</v>
-      </c>
-      <c r="C20" t="s">
-        <v>5</v>
-      </c>
-      <c r="D20" t="s">
-        <v>11</v>
-      </c>
-      <c r="E20" t="s">
-        <v>21</v>
-      </c>
-      <c r="F20" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="5">
-        <v>20</v>
-      </c>
-      <c r="B21">
-        <v>4364.527</v>
-      </c>
-      <c r="C21" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" t="s">
-        <v>18</v>
-      </c>
-      <c r="F21" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="5">
-        <v>21</v>
-      </c>
-      <c r="B22">
-        <v>4519.6019999999999</v>
-      </c>
-      <c r="C22" t="s">
-        <v>5</v>
-      </c>
-      <c r="D22" t="s">
-        <v>14</v>
-      </c>
-      <c r="E22" t="s">
-        <v>32</v>
-      </c>
-      <c r="F22" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="5">
-        <v>23</v>
-      </c>
-      <c r="B24">
-        <v>4489.0389999999998</v>
-      </c>
-      <c r="C24" t="s">
-        <v>7</v>
-      </c>
-      <c r="D24" t="s">
-        <v>9</v>
-      </c>
-      <c r="E24" t="s">
-        <v>18</v>
-      </c>
-      <c r="F24" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="5">
-        <v>24</v>
-      </c>
-      <c r="B25">
-        <v>4594.08</v>
-      </c>
-      <c r="C25" t="s">
-        <v>5</v>
-      </c>
-      <c r="D25" t="s">
-        <v>11</v>
-      </c>
-      <c r="E25" t="s">
-        <v>33</v>
-      </c>
-      <c r="F25" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="5">
-        <v>25</v>
-      </c>
-      <c r="B26">
-        <v>4442.9669999999996</v>
-      </c>
-      <c r="C26" t="s">
-        <v>7</v>
-      </c>
-      <c r="D26" t="s">
-        <v>13</v>
-      </c>
-      <c r="E26" t="s">
-        <v>18</v>
-      </c>
-      <c r="F26" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="5">
-        <v>26</v>
-      </c>
-      <c r="B27">
-        <v>4539.8639999999996</v>
-      </c>
-      <c r="C27" t="s">
-        <v>5</v>
-      </c>
-      <c r="D27" t="s">
-        <v>11</v>
-      </c>
-      <c r="E27" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="5">
-        <v>27</v>
-      </c>
-      <c r="B28">
-        <v>4422.3810000000003</v>
-      </c>
-      <c r="C28" t="s">
-        <v>35</v>
-      </c>
-      <c r="D28" t="s">
-        <v>13</v>
-      </c>
-      <c r="E28" t="s">
-        <v>18</v>
-      </c>
-      <c r="F28" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="5">
-        <v>28</v>
-      </c>
-      <c r="B29">
-        <v>4517.0129999999999</v>
-      </c>
-      <c r="C29" t="s">
-        <v>5</v>
-      </c>
-      <c r="D29" t="s">
-        <v>13</v>
-      </c>
-      <c r="E29" t="s">
-        <v>21</v>
-      </c>
-      <c r="F29" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="5">
-        <v>29</v>
-      </c>
-      <c r="B30">
-        <v>4270.7030000000004</v>
-      </c>
-      <c r="C30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E30" t="s">
-        <v>23</v>
-      </c>
-      <c r="F30" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="5">
-        <v>30</v>
-      </c>
-      <c r="B31">
-        <v>4365.1620000000003</v>
-      </c>
-      <c r="C31" t="s">
-        <v>5</v>
-      </c>
-      <c r="E31" t="s">
-        <v>21</v>
-      </c>
-      <c r="F31" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B23" s="5"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="5"/>
+      <c r="B24" s="5"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="5"/>
+      <c r="B25" s="5"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="5"/>
+      <c r="B26" s="5"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="5"/>
+      <c r="B27" s="5"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="5"/>
+      <c r="B28" s="5"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="5"/>
+      <c r="B29" s="5"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="5"/>
+      <c r="B30" s="5"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="5"/>
+      <c r="B31" s="5"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
+      <c r="B32" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/اختبار المتوسطه.xlsx
+++ b/docs/اختبار المتوسطه.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\MA-Waves\MA-Waves\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC8F33C1-4110-4C22-8B90-FEF7B931BD26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85218EA8-C6DF-4AF2-BBBF-55806F1BB8F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{7819BD92-4B63-487D-A2E5-7EFEA3C3CD0C}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="54">
   <si>
     <t>#</t>
   </si>
@@ -180,16 +180,32 @@
   </si>
   <si>
     <t>قاع متوسط لانه القاع الذي بعد الكسر</t>
+  </si>
+  <si>
+    <t>قاع صغير يجب ان يكون متوسط لانه القاع الذي بعد الكسر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">قمة صغير : المتوقع قمه متوسطخه لان القاع التالي كسر القاع السابق </t>
+  </si>
+  <si>
+    <t>قاع صغير : المتوقع قاع متوسط لانه القاع الذي بعد الكسر</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -217,12 +233,17 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -248,37 +269,58 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="4" fontId="2" fillId="3" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Neutral" xfId="1" builtinId="28"/>
+  <cellStyles count="3">
+    <cellStyle name="Bad" xfId="1" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="2" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="3">
@@ -819,7 +861,7 @@
       <c r="E8" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="13" t="s">
         <v>36</v>
       </c>
       <c r="G8" s="4" t="s">
@@ -863,7 +905,7 @@
       <c r="E10" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="13" t="s">
         <v>35</v>
       </c>
       <c r="G10" s="4" t="s">
@@ -928,7 +970,7 @@
       <c r="E13" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="13" t="s">
         <v>23</v>
       </c>
       <c r="G13" s="4" t="s">
@@ -951,7 +993,7 @@
       <c r="E14" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="13" t="s">
         <v>36</v>
       </c>
       <c r="G14" s="4" t="s">
@@ -995,7 +1037,7 @@
       <c r="E16" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="13" t="s">
         <v>35</v>
       </c>
       <c r="G16" s="4" t="s">
@@ -1102,7 +1144,7 @@
       <c r="E21" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="F21" s="13" t="s">
         <v>23</v>
       </c>
       <c r="G21" s="4" t="s">
@@ -1125,7 +1167,7 @@
       <c r="E22" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="F22" s="13" t="s">
         <v>36</v>
       </c>
       <c r="G22" s="4" t="s">
@@ -1148,7 +1190,7 @@
       <c r="E23" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="F23" s="13" t="s">
         <v>23</v>
       </c>
       <c r="G23" s="4" t="s">
@@ -1348,7 +1390,7 @@
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="11">
         <v>49716.51</v>
       </c>
       <c r="C2" s="4" t="s">
@@ -1371,7 +1413,7 @@
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="11">
         <v>51309.57</v>
       </c>
       <c r="C3" s="4" t="s">
@@ -1391,7 +1433,7 @@
       <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="11">
         <v>50851.87</v>
       </c>
       <c r="C4" s="4" t="s">
@@ -1411,7 +1453,7 @@
       <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="11">
         <v>51948.21</v>
       </c>
       <c r="C5" s="4" t="s">
@@ -1431,7 +1473,7 @@
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="11">
         <v>51646.63</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -1451,7 +1493,7 @@
       <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="11">
         <v>52203.67</v>
       </c>
       <c r="C7" s="4" t="s">
@@ -1471,7 +1513,7 @@
       <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="11">
         <v>51944.66</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -1491,7 +1533,7 @@
       <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="11">
         <v>52274.63</v>
       </c>
       <c r="C9" s="4" t="s">
@@ -1514,7 +1556,7 @@
       <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="11">
         <v>51446.01</v>
       </c>
       <c r="C10" s="4" t="s">
@@ -1537,7 +1579,7 @@
       <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="11">
         <v>51865.63</v>
       </c>
       <c r="C11" s="4" t="s">
@@ -1560,7 +1602,7 @@
       <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="11">
         <v>51376.98</v>
       </c>
       <c r="C12" s="4" t="s">
@@ -1580,7 +1622,7 @@
       <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="11">
         <v>51593.41</v>
       </c>
       <c r="C13" s="4" t="s">
@@ -1603,7 +1645,7 @@
       <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="11">
         <v>51302.47</v>
       </c>
       <c r="C14" s="4" t="s">
@@ -1626,7 +1668,7 @@
       <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B15" s="11">
         <v>51905.63</v>
       </c>
       <c r="C15" s="4" t="s">
@@ -1649,7 +1691,7 @@
       <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="11">
         <v>51290</v>
       </c>
       <c r="C16" s="4" t="s">
@@ -1672,7 +1714,7 @@
       <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="11">
         <v>51887.89</v>
       </c>
       <c r="C17" s="4" t="s">
@@ -1692,7 +1734,7 @@
       <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B18" s="11">
         <v>51543.74</v>
       </c>
       <c r="C18" s="4" t="s">
@@ -1712,7 +1754,7 @@
       <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19" s="11">
         <v>52249.79</v>
       </c>
       <c r="C19" s="4" t="s">
@@ -1732,19 +1774,19 @@
       <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="B20" s="6">
+      <c r="B20" s="11">
         <v>51743.360000000001</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="12" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1752,19 +1794,19 @@
       <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="B21" s="6">
+      <c r="B21" s="11">
         <v>52672.65</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="F21" s="12" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1772,7 +1814,7 @@
       <c r="A22" s="1">
         <v>21</v>
       </c>
-      <c r="B22" s="6"/>
+      <c r="B22" s="11"/>
       <c r="C22" s="4"/>
     </row>
   </sheetData>
@@ -1842,7 +1884,7 @@
       <c r="B3" s="1">
         <v>1</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="11">
         <v>49716.51</v>
       </c>
       <c r="D3" s="4" t="s">
@@ -1859,13 +1901,16 @@
       <c r="B4" s="1">
         <v>2</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="11">
         <v>51309.57</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>5</v>
       </c>
       <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1876,13 +1921,16 @@
       <c r="B5" s="1">
         <v>3</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="11">
         <v>50851.87</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1893,7 +1941,7 @@
       <c r="B6" s="1">
         <v>4</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="11">
         <v>51948.21</v>
       </c>
       <c r="D6" s="4" t="s">
@@ -1902,6 +1950,9 @@
       <c r="E6" t="s">
         <v>17</v>
       </c>
+      <c r="F6" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -1910,13 +1961,16 @@
       <c r="B7" s="1">
         <v>5</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="11">
         <v>51646.63</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1927,7 +1981,7 @@
       <c r="B8" s="1">
         <v>6</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="11">
         <v>52203.67</v>
       </c>
       <c r="D8" s="4" t="s">
@@ -1936,6 +1990,9 @@
       <c r="E8" t="s">
         <v>17</v>
       </c>
+      <c r="F8" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -1944,7 +2001,7 @@
       <c r="B9" s="1">
         <v>7</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="11">
         <v>51944.66</v>
       </c>
       <c r="D9" s="4" t="s">
@@ -1953,53 +2010,56 @@
       <c r="E9" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
+      <c r="F9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
         <v>8</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="5">
         <v>8</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="14">
         <v>52274.63</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="D10" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H10" s="7" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
+    <row r="11" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="5">
         <v>9</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="5">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="14">
         <v>51416.01</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="D11" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F11" t="s">
-        <v>16</v>
-      </c>
-      <c r="H11" t="s">
+      <c r="F11" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H11" s="7" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2010,13 +2070,16 @@
       <c r="B12" s="1">
         <v>10</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="11">
         <v>51865.63</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>5</v>
       </c>
       <c r="E12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2027,7 +2090,7 @@
       <c r="B13" s="1">
         <v>11</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="11">
         <v>51376.98</v>
       </c>
       <c r="D13" s="4" t="s">
@@ -2036,81 +2099,90 @@
       <c r="E13" t="s">
         <v>16</v>
       </c>
+      <c r="F13" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
+      <c r="A14" s="8">
         <v>12</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="8">
         <v>12</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="15">
         <v>51593.41</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="D14" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="10" t="s">
         <v>24</v>
       </c>
+      <c r="F14" s="10" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
+      <c r="A15" s="8">
         <v>13</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="8">
         <v>13</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="15">
         <v>51302.47</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
+      <c r="D15" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="5">
         <v>14</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="5">
         <v>14</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="14">
         <v>51905.63</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E16" s="5" t="s">
+      <c r="D16" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="G16" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="H16" s="7" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="1">
+    <row r="17" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="5">
         <v>15</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="5">
         <v>15</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="14">
         <v>51290</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="D17" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="7" t="s">
         <v>50</v>
       </c>
     </row>
@@ -2121,7 +2193,7 @@
       <c r="B18" s="1">
         <v>16</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="11">
         <v>51887.89</v>
       </c>
       <c r="D18" s="4" t="s">
@@ -2131,20 +2203,20 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="1">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19">
         <v>17</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19">
         <v>17</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19">
         <v>51543.74</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" s="5" t="s">
+      <c r="D19" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2155,7 +2227,7 @@
       <c r="B20" s="1">
         <v>18</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="11">
         <v>52249.79</v>
       </c>
       <c r="D20" s="4" t="s">
@@ -2172,7 +2244,7 @@
       <c r="B21" s="1">
         <v>19</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="11">
         <v>51743.360000000001</v>
       </c>
       <c r="D21" s="4" t="s">
@@ -2189,7 +2261,7 @@
       <c r="B22" s="1">
         <v>20</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="11">
         <v>52672.65</v>
       </c>
       <c r="D22" s="4" t="s">
@@ -2200,44 +2272,44 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="5"/>
-      <c r="B25" s="5"/>
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="5"/>
-      <c r="B26" s="5"/>
+      <c r="A26" s="7"/>
+      <c r="B26" s="7"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="5"/>
-      <c r="B27" s="5"/>
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="5"/>
-      <c r="B28" s="5"/>
+      <c r="A28" s="7"/>
+      <c r="B28" s="7"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="5"/>
-      <c r="B29" s="5"/>
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="5"/>
-      <c r="B30" s="5"/>
+      <c r="A30" s="7"/>
+      <c r="B30" s="7"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="5"/>
-      <c r="B31" s="5"/>
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="5"/>
-      <c r="B32" s="5"/>
+      <c r="A32" s="7"/>
+      <c r="B32" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/اختبار المتوسطه.xlsx
+++ b/docs/اختبار المتوسطه.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\MA-Waves\MA-Waves\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85218EA8-C6DF-4AF2-BBBF-55806F1BB8F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F640878A-8FF0-4F5C-9EE0-7D767ED79C26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{7819BD92-4B63-487D-A2E5-7EFEA3C3CD0C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{7819BD92-4B63-487D-A2E5-7EFEA3C3CD0C}"/>
   </bookViews>
   <sheets>
     <sheet name="هبوط" sheetId="3" r:id="rId1"/>
     <sheet name="صعود" sheetId="2" r:id="rId2"/>
     <sheet name="صعود 2 " sheetId="1" r:id="rId3"/>
+    <sheet name="هبوط 2US100 30 OC-21-NOV " sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="64">
   <si>
     <t>#</t>
   </si>
@@ -86,6 +87,9 @@
     <t>قاع صغيره</t>
   </si>
   <si>
+    <t>قمه</t>
+  </si>
+  <si>
     <t>قمه صغير</t>
   </si>
   <si>
@@ -189,6 +193,33 @@
   </si>
   <si>
     <t>قاع صغير : المتوقع قاع متوسط لانه القاع الذي بعد الكسر</t>
+  </si>
+  <si>
+    <t>متوسطه</t>
+  </si>
+  <si>
+    <t>صغير</t>
+  </si>
+  <si>
+    <t>يجب ان يمسع بقانون الفعاليه</t>
+  </si>
+  <si>
+    <t>يجب ان يمسح بقانون التتابع</t>
+  </si>
+  <si>
+    <t>صحيح</t>
+  </si>
+  <si>
+    <t>سحيح</t>
+  </si>
+  <si>
+    <t xml:space="preserve">رسم ك متوسط وهذا خاطئ لم يحدث كسر </t>
+  </si>
+  <si>
+    <t>رسم ك صغير يجب ان يكون متوسط لانه القاع الذي سبق الكسر</t>
+  </si>
+  <si>
+    <t>رسم ك صغير يجب ان يكون متوسط لانه القمه التي بعد الكسر</t>
   </si>
 </sst>
 </file>
@@ -694,7 +725,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -709,10 +740,10 @@
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -729,13 +760,13 @@
         <v>6</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -773,10 +804,10 @@
         <v>9</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G4" s="4"/>
     </row>
@@ -815,10 +846,10 @@
         <v>10</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G6" s="4"/>
     </row>
@@ -836,13 +867,13 @@
         <v>8</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -859,13 +890,13 @@
         <v>9</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -903,13 +934,13 @@
         <v>9</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -947,10 +978,10 @@
         <v>9</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G12" s="4"/>
     </row>
@@ -971,10 +1002,10 @@
         <v>15</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -991,13 +1022,13 @@
         <v>9</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1035,13 +1066,13 @@
         <v>11</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -1079,10 +1110,10 @@
         <v>9</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G18" s="4"/>
     </row>
@@ -1121,10 +1152,10 @@
         <v>9</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G20" s="4"/>
     </row>
@@ -1145,10 +1176,10 @@
         <v>16</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -1165,13 +1196,13 @@
         <v>13</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="30" x14ac:dyDescent="0.25">
@@ -1191,10 +1222,10 @@
         <v>16</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -1211,13 +1242,13 @@
         <v>11</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -1255,10 +1286,10 @@
         <v>11</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G26" s="4"/>
     </row>
@@ -1297,10 +1328,10 @@
         <v>12</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G28" s="4"/>
     </row>
@@ -1337,10 +1368,10 @@
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G30" s="4"/>
     </row>
@@ -1365,7 +1396,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
@@ -1383,7 +1414,7 @@
         <v>14</v>
       </c>
       <c r="G1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1397,16 +1428,16 @@
         <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1423,10 +1454,10 @@
         <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1440,7 +1471,7 @@
         <v>7</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
@@ -1480,7 +1511,7 @@
         <v>7</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E6" t="s">
         <v>16</v>
@@ -1520,7 +1551,7 @@
         <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E8" t="s">
         <v>16</v>
@@ -1543,13 +1574,13 @@
         <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1563,16 +1594,16 @@
         <v>7</v>
       </c>
       <c r="D10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E10" t="s">
         <v>16</v>
       </c>
       <c r="F10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1586,16 +1617,16 @@
         <v>5</v>
       </c>
       <c r="D11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1609,7 +1640,7 @@
         <v>7</v>
       </c>
       <c r="D12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E12" t="s">
         <v>18</v>
@@ -1632,13 +1663,13 @@
         <v>11</v>
       </c>
       <c r="E13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -1652,16 +1683,16 @@
         <v>7</v>
       </c>
       <c r="D14" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E14" t="s">
         <v>18</v>
       </c>
       <c r="F14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1675,16 +1706,16 @@
         <v>5</v>
       </c>
       <c r="D15" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15" t="s">
         <v>29</v>
-      </c>
-      <c r="E15" t="s">
-        <v>19</v>
-      </c>
-      <c r="F15" t="s">
-        <v>20</v>
-      </c>
-      <c r="G15" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1698,16 +1729,16 @@
         <v>7</v>
       </c>
       <c r="D16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1741,7 +1772,7 @@
         <v>7</v>
       </c>
       <c r="D18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E18" t="s">
         <v>18</v>
@@ -1764,10 +1795,10 @@
         <v>11</v>
       </c>
       <c r="E19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1781,7 +1812,7 @@
         <v>7</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E20" s="12" t="s">
         <v>18</v>
@@ -1804,10 +1835,10 @@
         <v>11</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1844,7 +1875,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -1862,12 +1893,12 @@
         <v>14</v>
       </c>
       <c r="H1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2" t="s">
@@ -1891,7 +1922,7 @@
         <v>7</v>
       </c>
       <c r="E3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2028,16 +2059,16 @@
         <v>5</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -2054,13 +2085,13 @@
         <v>7</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -2077,7 +2108,7 @@
         <v>5</v>
       </c>
       <c r="E12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F12" t="s">
         <v>17</v>
@@ -2117,10 +2148,10 @@
         <v>5</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -2140,7 +2171,7 @@
         <v>16</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -2157,16 +2188,16 @@
         <v>5</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:5" s="7" customFormat="1" x14ac:dyDescent="0.25">
@@ -2183,7 +2214,7 @@
         <v>7</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -2234,7 +2265,7 @@
         <v>5</v>
       </c>
       <c r="E20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -2317,4 +2348,325 @@
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A0CEE51-D789-43A5-978F-DA5C37A88868}">
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.42578125" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="3" max="3" width="39.85546875" customWidth="1"/>
+    <col min="5" max="5" width="46" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11">
+        <v>26259.29</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="11">
+        <v>25713.11</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="11">
+        <v>26136.6</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="11">
+        <v>25166.29</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="11">
+        <v>25427.040000000001</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="11">
+        <v>25284.85</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>5</v>
+      </c>
+      <c r="B8" s="11">
+        <v>25759.49</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>6</v>
+      </c>
+      <c r="B9" s="11">
+        <v>25053.4</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>7</v>
+      </c>
+      <c r="B10" s="11">
+        <v>25242.19</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>8</v>
+      </c>
+      <c r="B11" s="11">
+        <v>24611.87</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>9</v>
+      </c>
+      <c r="B12" s="11">
+        <v>25676.959999999999</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>10</v>
+      </c>
+      <c r="B13" s="11">
+        <v>25389.34</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>11</v>
+      </c>
+      <c r="B14" s="11">
+        <v>25727.59</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>12</v>
+      </c>
+      <c r="B15" s="11">
+        <v>24536.68</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>13</v>
+      </c>
+      <c r="B16" s="11">
+        <v>25269.98</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>14</v>
+      </c>
+      <c r="B17" s="11">
+        <v>24306.46</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>15</v>
+      </c>
+      <c r="B18" s="11">
+        <v>25219.98</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>